--- a/Data/2017_F013B4_CO_ITR/2017_F013B4_CO_ITR_SoilAnalysis.xlsx
+++ b/Data/2017_F013B4_CO_ITR/2017_F013B4_CO_ITR_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2017_F013B4_CO_ITR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D074BA8-29B4-4B13-A4E0-7972179C726F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB56DF44-4078-40B0-A52D-B7C44607D6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-28050" windowWidth="17910" windowHeight="25080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1665" yWindow="-26460" windowWidth="27270" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="7" r:id="rId1"/>
@@ -815,9 +815,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2013d260EM38</t>
-  </si>
-  <si>
     <t>2015d118EM38</t>
   </si>
   <si>
@@ -1857,6 +1854,9 @@
   </si>
   <si>
     <t>2016-p03-1</t>
+  </si>
+  <si>
+    <t>2013d260EM38V</t>
   </si>
 </sst>
 </file>
@@ -2700,13 +2700,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -2717,7 +2717,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C2">
         <v>408928.783999999</v>
@@ -2734,7 +2734,7 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C3">
         <v>408927.88109999901</v>
@@ -2751,7 +2751,7 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C4">
         <v>408927.42930000002</v>
@@ -2768,7 +2768,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C5">
         <v>408926.97979999898</v>
@@ -2785,7 +2785,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C6">
         <v>408901.33329999901</v>
@@ -2802,7 +2802,7 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C7">
         <v>408900.44150000002</v>
@@ -2819,7 +2819,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C8">
         <v>408899.99949999899</v>
@@ -2836,7 +2836,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C9">
         <v>408899.580599999</v>
@@ -2853,7 +2853,7 @@
         <v>151</v>
       </c>
       <c r="B10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C10">
         <v>408879.86940000003</v>
@@ -2870,7 +2870,7 @@
         <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C11">
         <v>408879.400499999</v>
@@ -2887,7 +2887,7 @@
         <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C12">
         <v>408878.89939999901</v>
@@ -2904,7 +2904,7 @@
         <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C13">
         <v>408877.92340000003</v>
@@ -2921,7 +2921,7 @@
         <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C14">
         <v>408845.46089999902</v>
@@ -2938,7 +2938,7 @@
         <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C15">
         <v>408850.18070000003</v>
@@ -2955,7 +2955,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C16">
         <v>408844.56319999899</v>
@@ -2972,7 +2972,7 @@
         <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C17">
         <v>408849.70020000002</v>
@@ -2989,7 +2989,7 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C18">
         <v>408844.13500000001</v>
@@ -3006,7 +3006,7 @@
         <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C19">
         <v>408849.219199999</v>
@@ -3023,7 +3023,7 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C20">
         <v>408843.68329999998</v>
@@ -3040,7 +3040,7 @@
         <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C21">
         <v>408848.231299999</v>
@@ -3057,7 +3057,7 @@
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C22">
         <v>408817.00829999999</v>
@@ -3074,7 +3074,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C23">
         <v>408816.12689999898</v>
@@ -3091,7 +3091,7 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24">
         <v>408815.666399999</v>
@@ -3108,7 +3108,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C25">
         <v>408815.248499999</v>
@@ -3125,7 +3125,7 @@
         <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C26">
         <v>408788.581799999</v>
@@ -3142,7 +3142,7 @@
         <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C27">
         <v>408793.35800000001</v>
@@ -3159,7 +3159,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C28">
         <v>408787.67560000002</v>
@@ -3176,7 +3176,7 @@
         <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C29">
         <v>408792.866099999</v>
@@ -3193,7 +3193,7 @@
         <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C30">
         <v>408787.222799999</v>
@@ -3210,7 +3210,7 @@
         <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C31">
         <v>408792.38530000002</v>
@@ -3227,7 +3227,7 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C32">
         <v>408786.80749999901</v>
@@ -3244,7 +3244,7 @@
         <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C33">
         <v>408791.43050000002</v>
@@ -3261,7 +3261,7 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C34">
         <v>408760.11839999899</v>
@@ -3278,7 +3278,7 @@
         <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C35">
         <v>408759.24219999899</v>
@@ -3295,7 +3295,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C36">
         <v>408758.807399999</v>
@@ -3312,7 +3312,7 @@
         <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C37">
         <v>408758.367499999</v>
@@ -3329,7 +3329,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3346,7 +3346,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3363,7 +3363,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3380,7 +3380,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3397,7 +3397,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3414,7 +3414,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3431,7 +3431,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3448,7 +3448,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3465,7 +3465,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3482,7 +3482,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3499,7 +3499,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3516,7 +3516,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3533,7 +3533,7 @@
         <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C50">
         <v>408734.69020000001</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C51">
         <v>408734.44760000001</v>
@@ -3567,7 +3567,7 @@
         <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C52">
         <v>408728.347899999</v>
@@ -3584,7 +3584,7 @@
         <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C53">
         <v>408728.57990000001</v>
@@ -3601,7 +3601,7 @@
         <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C54">
         <v>408734.16200000001</v>
@@ -3618,7 +3618,7 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C55">
         <v>408733.81439999898</v>
@@ -3635,7 +3635,7 @@
         <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C56">
         <v>408727.74089999998</v>
@@ -3652,7 +3652,7 @@
         <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C57">
         <v>408727.98920000001</v>
@@ -3669,7 +3669,7 @@
         <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C58">
         <v>408733.443499999</v>
@@ -3686,7 +3686,7 @@
         <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C59">
         <v>408727.3763</v>
@@ -3703,7 +3703,7 @@
         <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C60">
         <v>408732.84250000003</v>
@@ -3720,7 +3720,7 @@
         <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C61">
         <v>408726.75140000001</v>
@@ -3737,7 +3737,7 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C62">
         <v>408720.46580000001</v>
@@ -3754,7 +3754,7 @@
         <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C63">
         <v>408720.19679999899</v>
@@ -3771,7 +3771,7 @@
         <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C64">
         <v>408714.09700000001</v>
@@ -3788,7 +3788,7 @@
         <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C65">
         <v>408714.40309999901</v>
@@ -3805,7 +3805,7 @@
         <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C66">
         <v>408719.8885</v>
@@ -3822,7 +3822,7 @@
         <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C67">
         <v>408719.60830000002</v>
@@ -3839,7 +3839,7 @@
         <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C68">
         <v>408713.53340000001</v>
@@ -3856,7 +3856,7 @@
         <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C69">
         <v>408713.790299999</v>
@@ -3873,7 +3873,7 @@
         <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C70">
         <v>408719.22999999899</v>
@@ -3890,7 +3890,7 @@
         <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C71">
         <v>408713.13880000002</v>
@@ -3907,7 +3907,7 @@
         <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C72">
         <v>408718.61729999899</v>
@@ -3924,7 +3924,7 @@
         <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C73">
         <v>408712.455599999</v>
@@ -3941,7 +3941,7 @@
         <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C74">
         <v>408706.2476</v>
@@ -3958,7 +3958,7 @@
         <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C75">
         <v>408705.94109999901</v>
@@ -3975,7 +3975,7 @@
         <v>129</v>
       </c>
       <c r="B76" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C76">
         <v>408699.85230000003</v>
@@ -3992,7 +3992,7 @@
         <v>130</v>
       </c>
       <c r="B77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C77">
         <v>408700.13030000002</v>
@@ -4009,7 +4009,7 @@
         <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C78">
         <v>408705.62539999897</v>
@@ -4026,7 +4026,7 @@
         <v>118</v>
       </c>
       <c r="B79" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C79">
         <v>408705.38500000001</v>
@@ -4043,7 +4043,7 @@
         <v>127</v>
       </c>
       <c r="B80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C80">
         <v>408699.26530000003</v>
@@ -4060,7 +4060,7 @@
         <v>128</v>
       </c>
       <c r="B81" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C81">
         <v>408699.535299999</v>
@@ -4077,7 +4077,7 @@
         <v>119</v>
       </c>
       <c r="B82" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C82">
         <v>408704.99829999899</v>
@@ -4094,7 +4094,7 @@
         <v>126</v>
       </c>
       <c r="B83" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C83">
         <v>408698.93699999899</v>
@@ -4111,7 +4111,7 @@
         <v>121</v>
       </c>
       <c r="B84" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C84">
         <v>408704.38349999901</v>
@@ -4128,7 +4128,7 @@
         <v>124</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C85">
         <v>408698.26829999901</v>
@@ -4158,13 +4158,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -4175,13 +4175,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E2" t="s">
         <v>257</v>
@@ -4192,13 +4192,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E3" t="s">
         <v>256</v>
@@ -4209,13 +4209,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E4" t="s">
         <v>255</v>
@@ -4226,13 +4226,13 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E5" t="s">
         <v>254</v>
@@ -4243,13 +4243,13 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E6" t="s">
         <v>253</v>
@@ -4260,13 +4260,13 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E7" t="s">
         <v>252</v>
@@ -4277,13 +4277,13 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E8" t="s">
         <v>251</v>
@@ -4294,13 +4294,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E9" t="s">
         <v>250</v>
@@ -4311,13 +4311,13 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E10" t="s">
         <v>249</v>
@@ -4328,13 +4328,13 @@
         <v>154</v>
       </c>
       <c r="B11" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E11" t="s">
         <v>248</v>
@@ -4345,13 +4345,13 @@
         <v>155</v>
       </c>
       <c r="B12" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E12" t="s">
         <v>247</v>
@@ -4362,13 +4362,13 @@
         <v>156</v>
       </c>
       <c r="B13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E13" t="s">
         <v>246</v>
@@ -4379,13 +4379,13 @@
         <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E14" t="s">
         <v>245</v>
@@ -4396,13 +4396,13 @@
         <v>158</v>
       </c>
       <c r="B15" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E15" t="s">
         <v>244</v>
@@ -4413,13 +4413,13 @@
         <v>159</v>
       </c>
       <c r="B16" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E16" t="s">
         <v>243</v>
@@ -4430,13 +4430,13 @@
         <v>160</v>
       </c>
       <c r="B17" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E17" t="s">
         <v>242</v>
@@ -4447,13 +4447,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E18" t="s">
         <v>241</v>
@@ -4464,13 +4464,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E19" t="s">
         <v>240</v>
@@ -4481,13 +4481,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E20" t="s">
         <v>239</v>
@@ -4498,13 +4498,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E21" t="s">
         <v>238</v>
@@ -4515,13 +4515,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E22" t="s">
         <v>237</v>
@@ -4532,13 +4532,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E23" t="s">
         <v>236</v>
@@ -4549,13 +4549,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E24" t="s">
         <v>235</v>
@@ -4566,13 +4566,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E25" t="s">
         <v>234</v>
@@ -4583,13 +4583,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E26" t="s">
         <v>233</v>
@@ -4600,13 +4600,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E27" t="s">
         <v>232</v>
@@ -4617,13 +4617,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E28" t="s">
         <v>231</v>
@@ -4634,13 +4634,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E29" t="s">
         <v>230</v>
@@ -4651,13 +4651,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E30" t="s">
         <v>229</v>
@@ -4668,13 +4668,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E31" t="s">
         <v>228</v>
@@ -4685,13 +4685,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E32" t="s">
         <v>227</v>
@@ -4702,13 +4702,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E33" t="s">
         <v>226</v>
@@ -4719,13 +4719,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E34" t="s">
         <v>225</v>
@@ -4736,13 +4736,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E35" t="s">
         <v>224</v>
@@ -4753,13 +4753,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E36" t="s">
         <v>223</v>
@@ -4770,13 +4770,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E37" t="s">
         <v>222</v>
@@ -4787,13 +4787,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -4804,13 +4804,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E39" t="s">
         <v>220</v>
@@ -4821,13 +4821,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E40" t="s">
         <v>219</v>
@@ -4838,13 +4838,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E41" t="s">
         <v>218</v>
@@ -4855,13 +4855,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E42" t="s">
         <v>217</v>
@@ -4872,13 +4872,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E43" t="s">
         <v>216</v>
@@ -4889,13 +4889,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E44" t="s">
         <v>215</v>
@@ -4906,13 +4906,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E45" t="s">
         <v>214</v>
@@ -4923,13 +4923,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E46" t="s">
         <v>213</v>
@@ -4940,13 +4940,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E47" t="s">
         <v>212</v>
@@ -4957,13 +4957,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E48" t="s">
         <v>211</v>
@@ -4974,13 +4974,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E49" t="s">
         <v>210</v>
@@ -4991,13 +4991,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E50" t="s">
         <v>209</v>
@@ -5008,13 +5008,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E51" t="s">
         <v>208</v>
@@ -5025,13 +5025,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E52" t="s">
         <v>207</v>
@@ -5042,13 +5042,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E53" t="s">
         <v>206</v>
@@ -5059,13 +5059,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E54" t="s">
         <v>205</v>
@@ -5076,13 +5076,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E55" t="s">
         <v>204</v>
@@ -5093,13 +5093,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E56" t="s">
         <v>203</v>
@@ -5110,13 +5110,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E57" t="s">
         <v>202</v>
@@ -5127,13 +5127,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E58" t="s">
         <v>201</v>
@@ -5144,13 +5144,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E59" t="s">
         <v>200</v>
@@ -5161,13 +5161,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E60" t="s">
         <v>199</v>
@@ -5178,13 +5178,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E61" t="s">
         <v>198</v>
@@ -5195,13 +5195,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E62" t="s">
         <v>197</v>
@@ -5212,13 +5212,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E63" t="s">
         <v>196</v>
@@ -5229,13 +5229,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E64" t="s">
         <v>195</v>
@@ -5246,13 +5246,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E65" t="s">
         <v>194</v>
@@ -5276,211 +5276,211 @@
         <v>192</v>
       </c>
       <c r="C1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>277</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>278</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>279</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>280</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>281</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>282</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>283</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>284</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>285</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>286</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>287</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>288</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>289</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>291</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>292</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>293</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>294</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>295</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>296</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>297</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>298</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>299</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>300</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>301</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>302</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>303</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>304</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>305</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>306</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>307</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>308</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>309</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>310</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>311</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>312</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>313</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>314</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>315</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>316</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>317</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>318</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>319</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>320</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>321</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>322</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>323</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>324</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>325</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>326</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -45950,211 +45950,211 @@
         <v>258</v>
       </c>
       <c r="C1" t="s">
+        <v>606</v>
+      </c>
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>277</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>278</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>279</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>280</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>281</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>282</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>283</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>284</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>285</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>286</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>287</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>288</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>289</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>291</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>292</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>293</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>294</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>295</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>296</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>297</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>298</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>299</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>300</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>301</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>302</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>303</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>304</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>305</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>306</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>307</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>308</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>309</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>310</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>311</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>312</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>313</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>314</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>315</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>316</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>317</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>318</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>319</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>320</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>321</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>322</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>323</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>324</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>325</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>326</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">

--- a/Data/2017_F013B4_CO_ITR/2017_F013B4_CO_ITR_SoilAnalysis.xlsx
+++ b/Data/2017_F013B4_CO_ITR/2017_F013B4_CO_ITR_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2017_F013B4_CO_ITR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59D090A-BCFE-429B-B813-529FED27F064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF5EC1B-3473-440D-976C-36D41BAC93BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1485" yWindow="-24615" windowWidth="17775" windowHeight="24285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1815" yWindow="-28410" windowWidth="16335" windowHeight="23370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="7" r:id="rId1"/>
@@ -815,12 +815,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2015d118EM38</t>
-  </si>
-  <si>
-    <t>2015d119EM38</t>
-  </si>
-  <si>
     <t>SLSND015</t>
   </si>
   <si>
@@ -1857,6 +1851,12 @@
   </si>
   <si>
     <t>2013d260EM38V</t>
+  </si>
+  <si>
+    <t>2015d118EM38V</t>
+  </si>
+  <si>
+    <t>2015d119EM38V</t>
   </si>
 </sst>
 </file>
@@ -2700,13 +2700,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -2717,7 +2717,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C2">
         <v>408928.783999999</v>
@@ -2734,7 +2734,7 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C3">
         <v>408927.88109999901</v>
@@ -2751,7 +2751,7 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C4">
         <v>408927.42930000002</v>
@@ -2768,7 +2768,7 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C5">
         <v>408926.97979999898</v>
@@ -2785,7 +2785,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C6">
         <v>408901.33329999901</v>
@@ -2802,7 +2802,7 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C7">
         <v>408900.44150000002</v>
@@ -2819,7 +2819,7 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C8">
         <v>408899.99949999899</v>
@@ -2836,7 +2836,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C9">
         <v>408899.580599999</v>
@@ -2853,7 +2853,7 @@
         <v>151</v>
       </c>
       <c r="B10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C10">
         <v>408879.86940000003</v>
@@ -2870,7 +2870,7 @@
         <v>152</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C11">
         <v>408879.400499999</v>
@@ -2887,7 +2887,7 @@
         <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C12">
         <v>408878.89939999901</v>
@@ -2904,7 +2904,7 @@
         <v>155</v>
       </c>
       <c r="B13" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C13">
         <v>408877.92340000003</v>
@@ -2921,7 +2921,7 @@
         <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C14">
         <v>408845.46089999902</v>
@@ -2938,7 +2938,7 @@
         <v>156</v>
       </c>
       <c r="B15" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C15">
         <v>408850.18070000003</v>
@@ -2955,7 +2955,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C16">
         <v>408844.56319999899</v>
@@ -2972,7 +2972,7 @@
         <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C17">
         <v>408849.70020000002</v>
@@ -2989,7 +2989,7 @@
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C18">
         <v>408844.13500000001</v>
@@ -3006,7 +3006,7 @@
         <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C19">
         <v>408849.219199999</v>
@@ -3023,7 +3023,7 @@
         <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C20">
         <v>408843.68329999998</v>
@@ -3040,7 +3040,7 @@
         <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C21">
         <v>408848.231299999</v>
@@ -3057,7 +3057,7 @@
         <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C22">
         <v>408817.00829999999</v>
@@ -3074,7 +3074,7 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C23">
         <v>408816.12689999898</v>
@@ -3091,7 +3091,7 @@
         <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C24">
         <v>408815.666399999</v>
@@ -3108,7 +3108,7 @@
         <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C25">
         <v>408815.248499999</v>
@@ -3125,7 +3125,7 @@
         <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C26">
         <v>408788.581799999</v>
@@ -3142,7 +3142,7 @@
         <v>166</v>
       </c>
       <c r="B27" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C27">
         <v>408793.35800000001</v>
@@ -3159,7 +3159,7 @@
         <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C28">
         <v>408787.67560000002</v>
@@ -3176,7 +3176,7 @@
         <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C29">
         <v>408792.866099999</v>
@@ -3193,7 +3193,7 @@
         <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C30">
         <v>408787.222799999</v>
@@ -3210,7 +3210,7 @@
         <v>168</v>
       </c>
       <c r="B31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C31">
         <v>408792.38530000002</v>
@@ -3227,7 +3227,7 @@
         <v>53</v>
       </c>
       <c r="B32" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C32">
         <v>408786.80749999901</v>
@@ -3244,7 +3244,7 @@
         <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C33">
         <v>408791.43050000002</v>
@@ -3261,7 +3261,7 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C34">
         <v>408760.11839999899</v>
@@ -3278,7 +3278,7 @@
         <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C35">
         <v>408759.24219999899</v>
@@ -3295,7 +3295,7 @@
         <v>57</v>
       </c>
       <c r="B36" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C36">
         <v>408758.807399999</v>
@@ -3312,7 +3312,7 @@
         <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C37">
         <v>408758.367499999</v>
@@ -3329,7 +3329,7 @@
         <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C38">
         <v>408748.9094</v>
@@ -3346,7 +3346,7 @@
         <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C39">
         <v>408748.6594</v>
@@ -3363,7 +3363,7 @@
         <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C40">
         <v>408742.57679999899</v>
@@ -3380,7 +3380,7 @@
         <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C41">
         <v>408742.84710000001</v>
@@ -3397,7 +3397,7 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C42">
         <v>408748.33390000003</v>
@@ -3414,7 +3414,7 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C43">
         <v>408747.98800000001</v>
@@ -3431,7 +3431,7 @@
         <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C44">
         <v>408741.9215</v>
@@ -3448,7 +3448,7 @@
         <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C45">
         <v>408742.204399999</v>
@@ -3465,7 +3465,7 @@
         <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C46">
         <v>408747.652899999</v>
@@ -3482,7 +3482,7 @@
         <v>78</v>
       </c>
       <c r="B47" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C47">
         <v>408741.583099999</v>
@@ -3499,7 +3499,7 @@
         <v>73</v>
       </c>
       <c r="B48" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C48">
         <v>408747.01990000001</v>
@@ -3516,7 +3516,7 @@
         <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C49">
         <v>408740.96580000001</v>
@@ -3533,7 +3533,7 @@
         <v>83</v>
       </c>
       <c r="B50" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C50">
         <v>408734.69020000001</v>
@@ -3550,7 +3550,7 @@
         <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C51">
         <v>408734.44760000001</v>
@@ -3567,7 +3567,7 @@
         <v>97</v>
       </c>
       <c r="B52" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C52">
         <v>408728.347899999</v>
@@ -3584,7 +3584,7 @@
         <v>98</v>
       </c>
       <c r="B53" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C53">
         <v>408728.57990000001</v>
@@ -3601,7 +3601,7 @@
         <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C54">
         <v>408734.16200000001</v>
@@ -3618,7 +3618,7 @@
         <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C55">
         <v>408733.81439999898</v>
@@ -3635,7 +3635,7 @@
         <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C56">
         <v>408727.74089999998</v>
@@ -3652,7 +3652,7 @@
         <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C57">
         <v>408727.98920000001</v>
@@ -3669,7 +3669,7 @@
         <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C58">
         <v>408733.443499999</v>
@@ -3686,7 +3686,7 @@
         <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C59">
         <v>408727.3763</v>
@@ -3703,7 +3703,7 @@
         <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C60">
         <v>408732.84250000003</v>
@@ -3720,7 +3720,7 @@
         <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C61">
         <v>408726.75140000001</v>
@@ -3737,7 +3737,7 @@
         <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C62">
         <v>408720.46580000001</v>
@@ -3754,7 +3754,7 @@
         <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C63">
         <v>408720.19679999899</v>
@@ -3771,7 +3771,7 @@
         <v>113</v>
       </c>
       <c r="B64" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C64">
         <v>408714.09700000001</v>
@@ -3788,7 +3788,7 @@
         <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C65">
         <v>408714.40309999901</v>
@@ -3805,7 +3805,7 @@
         <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C66">
         <v>408719.8885</v>
@@ -3822,7 +3822,7 @@
         <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C67">
         <v>408719.60830000002</v>
@@ -3839,7 +3839,7 @@
         <v>111</v>
       </c>
       <c r="B68" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C68">
         <v>408713.53340000001</v>
@@ -3856,7 +3856,7 @@
         <v>112</v>
       </c>
       <c r="B69" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C69">
         <v>408713.790299999</v>
@@ -3873,7 +3873,7 @@
         <v>103</v>
       </c>
       <c r="B70" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C70">
         <v>408719.22999999899</v>
@@ -3890,7 +3890,7 @@
         <v>110</v>
       </c>
       <c r="B71" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C71">
         <v>408713.13880000002</v>
@@ -3907,7 +3907,7 @@
         <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C72">
         <v>408718.61729999899</v>
@@ -3924,7 +3924,7 @@
         <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C73">
         <v>408712.455599999</v>
@@ -3941,7 +3941,7 @@
         <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C74">
         <v>408706.2476</v>
@@ -3958,7 +3958,7 @@
         <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C75">
         <v>408705.94109999901</v>
@@ -3975,7 +3975,7 @@
         <v>129</v>
       </c>
       <c r="B76" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C76">
         <v>408699.85230000003</v>
@@ -3992,7 +3992,7 @@
         <v>130</v>
       </c>
       <c r="B77" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C77">
         <v>408700.13030000002</v>
@@ -4009,7 +4009,7 @@
         <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C78">
         <v>408705.62539999897</v>
@@ -4026,7 +4026,7 @@
         <v>118</v>
       </c>
       <c r="B79" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C79">
         <v>408705.38500000001</v>
@@ -4043,7 +4043,7 @@
         <v>127</v>
       </c>
       <c r="B80" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C80">
         <v>408699.26530000003</v>
@@ -4060,7 +4060,7 @@
         <v>128</v>
       </c>
       <c r="B81" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C81">
         <v>408699.535299999</v>
@@ -4077,7 +4077,7 @@
         <v>119</v>
       </c>
       <c r="B82" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C82">
         <v>408704.99829999899</v>
@@ -4094,7 +4094,7 @@
         <v>126</v>
       </c>
       <c r="B83" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C83">
         <v>408698.93699999899</v>
@@ -4111,7 +4111,7 @@
         <v>121</v>
       </c>
       <c r="B84" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C84">
         <v>408704.38349999901</v>
@@ -4128,7 +4128,7 @@
         <v>124</v>
       </c>
       <c r="B85" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C85">
         <v>408698.26829999901</v>
@@ -4158,13 +4158,13 @@
         <v>193</v>
       </c>
       <c r="B1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E1" t="s">
         <v>258</v>
@@ -4175,13 +4175,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E2" t="s">
         <v>257</v>
@@ -4192,13 +4192,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E3" t="s">
         <v>256</v>
@@ -4209,13 +4209,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E4" t="s">
         <v>255</v>
@@ -4226,13 +4226,13 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E5" t="s">
         <v>254</v>
@@ -4243,13 +4243,13 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E6" t="s">
         <v>253</v>
@@ -4260,13 +4260,13 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E7" t="s">
         <v>252</v>
@@ -4277,13 +4277,13 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E8" t="s">
         <v>251</v>
@@ -4294,13 +4294,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E9" t="s">
         <v>250</v>
@@ -4311,13 +4311,13 @@
         <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E10" t="s">
         <v>249</v>
@@ -4328,13 +4328,13 @@
         <v>154</v>
       </c>
       <c r="B11" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E11" t="s">
         <v>248</v>
@@ -4345,13 +4345,13 @@
         <v>155</v>
       </c>
       <c r="B12" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E12" t="s">
         <v>247</v>
@@ -4362,13 +4362,13 @@
         <v>156</v>
       </c>
       <c r="B13" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E13" t="s">
         <v>246</v>
@@ -4379,13 +4379,13 @@
         <v>157</v>
       </c>
       <c r="B14" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E14" t="s">
         <v>245</v>
@@ -4396,13 +4396,13 @@
         <v>158</v>
       </c>
       <c r="B15" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E15" t="s">
         <v>244</v>
@@ -4413,13 +4413,13 @@
         <v>159</v>
       </c>
       <c r="B16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E16" t="s">
         <v>243</v>
@@ -4430,13 +4430,13 @@
         <v>160</v>
       </c>
       <c r="B17" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E17" t="s">
         <v>242</v>
@@ -4447,13 +4447,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E18" t="s">
         <v>241</v>
@@ -4464,13 +4464,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E19" t="s">
         <v>240</v>
@@ -4481,13 +4481,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E20" t="s">
         <v>239</v>
@@ -4498,13 +4498,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E21" t="s">
         <v>238</v>
@@ -4515,13 +4515,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E22" t="s">
         <v>237</v>
@@ -4532,13 +4532,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E23" t="s">
         <v>236</v>
@@ -4549,13 +4549,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E24" t="s">
         <v>235</v>
@@ -4566,13 +4566,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E25" t="s">
         <v>234</v>
@@ -4583,13 +4583,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E26" t="s">
         <v>233</v>
@@ -4600,13 +4600,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E27" t="s">
         <v>232</v>
@@ -4617,13 +4617,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E28" t="s">
         <v>231</v>
@@ -4634,13 +4634,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E29" t="s">
         <v>230</v>
@@ -4651,13 +4651,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E30" t="s">
         <v>229</v>
@@ -4668,13 +4668,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E31" t="s">
         <v>228</v>
@@ -4685,13 +4685,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E32" t="s">
         <v>227</v>
@@ -4702,13 +4702,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E33" t="s">
         <v>226</v>
@@ -4719,13 +4719,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E34" t="s">
         <v>225</v>
@@ -4736,13 +4736,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E35" t="s">
         <v>224</v>
@@ -4753,13 +4753,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E36" t="s">
         <v>223</v>
@@ -4770,13 +4770,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E37" t="s">
         <v>222</v>
@@ -4787,13 +4787,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E38" t="s">
         <v>221</v>
@@ -4804,13 +4804,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E39" t="s">
         <v>220</v>
@@ -4821,13 +4821,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E40" t="s">
         <v>219</v>
@@ -4838,13 +4838,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E41" t="s">
         <v>218</v>
@@ -4855,13 +4855,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E42" t="s">
         <v>217</v>
@@ -4872,13 +4872,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E43" t="s">
         <v>216</v>
@@ -4889,13 +4889,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E44" t="s">
         <v>215</v>
@@ -4906,13 +4906,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E45" t="s">
         <v>214</v>
@@ -4923,13 +4923,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E46" t="s">
         <v>213</v>
@@ -4940,13 +4940,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E47" t="s">
         <v>212</v>
@@ -4957,13 +4957,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E48" t="s">
         <v>211</v>
@@ -4974,13 +4974,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E49" t="s">
         <v>210</v>
@@ -4991,13 +4991,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E50" t="s">
         <v>209</v>
@@ -5008,13 +5008,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E51" t="s">
         <v>208</v>
@@ -5025,13 +5025,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E52" t="s">
         <v>207</v>
@@ -5042,13 +5042,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E53" t="s">
         <v>206</v>
@@ -5059,13 +5059,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E54" t="s">
         <v>205</v>
@@ -5076,13 +5076,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E55" t="s">
         <v>204</v>
@@ -5093,13 +5093,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E56" t="s">
         <v>203</v>
@@ -5110,13 +5110,13 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E57" t="s">
         <v>202</v>
@@ -5127,13 +5127,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E58" t="s">
         <v>201</v>
@@ -5144,13 +5144,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E59" t="s">
         <v>200</v>
@@ -5161,13 +5161,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E60" t="s">
         <v>199</v>
@@ -5178,13 +5178,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E61" t="s">
         <v>198</v>
@@ -5195,13 +5195,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E62" t="s">
         <v>197</v>
@@ -5212,13 +5212,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E63" t="s">
         <v>196</v>
@@ -5229,13 +5229,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E64" t="s">
         <v>195</v>
@@ -5246,13 +5246,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E65" t="s">
         <v>194</v>
@@ -5276,211 +5276,211 @@
         <v>192</v>
       </c>
       <c r="C1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1" t="s">
         <v>606</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>264</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>265</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>266</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>267</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>268</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>270</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>271</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>273</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>274</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>275</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>276</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>277</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>278</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>279</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>280</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>281</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>282</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>283</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>284</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>285</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>286</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>287</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>288</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>289</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>290</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>291</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>292</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>293</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>294</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>295</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>296</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>297</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>298</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>299</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>300</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>301</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>302</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>303</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>304</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>305</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>306</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>307</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>308</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>309</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>310</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>311</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>312</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>313</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>314</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>315</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>316</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>317</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>318</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>319</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>320</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>321</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>322</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>323</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>324</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>325</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -45950,211 +45950,211 @@
         <v>258</v>
       </c>
       <c r="C1" t="s">
+        <v>604</v>
+      </c>
+      <c r="D1" t="s">
+        <v>605</v>
+      </c>
+      <c r="E1" t="s">
         <v>606</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>263</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>264</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>265</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>266</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>267</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>268</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>270</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>271</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>273</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>274</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>275</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>276</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>277</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>278</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>279</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>280</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>281</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>282</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>283</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>284</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>285</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>286</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>287</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>288</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>289</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>290</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>291</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>292</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>293</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>294</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>295</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>296</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>297</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>298</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>299</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>300</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>301</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>302</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>303</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>304</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>305</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>306</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>307</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>308</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>309</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>310</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>311</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>312</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>313</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>314</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>315</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>316</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>317</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>318</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>319</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>320</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>321</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>322</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>323</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>324</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>325</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
